--- a/data/stx_xlsx/ORRON.ST.xlsx
+++ b/data/stx_xlsx/ORRON.ST.xlsx
@@ -11799,13 +11799,34 @@
       <c r="P43" s="16">
         <v>13921.12</v>
       </c>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
-      <c r="S43" s="16"/>
-      <c r="T43" s="16"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="16"/>
-      <c r="W43" s="16"/>
+      <c r="Q43" s="16">
+        <f t="shared" ref="Q43:W43" si="1">SUM(Q60,Q64)</f>
+        <v>8351.08</v>
+      </c>
+      <c r="R43" s="16">
+        <f t="shared" si="1"/>
+        <v>11640.8</v>
+      </c>
+      <c r="S43" s="16">
+        <f t="shared" si="1"/>
+        <v>13946.19</v>
+      </c>
+      <c r="T43" s="16">
+        <f t="shared" si="1"/>
+        <v>14108.69</v>
+      </c>
+      <c r="U43" s="16">
+        <f t="shared" si="1"/>
+        <v>7287.92</v>
+      </c>
+      <c r="V43" s="16">
+        <f t="shared" si="1"/>
+        <v>4868.11</v>
+      </c>
+      <c r="W43" s="16">
+        <f t="shared" si="1"/>
+        <v>3108.02</v>
+      </c>
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
